--- a/results/demand/P4_full_fixed_TEAM_HIGH_DEMAND/results.xlsx
+++ b/results/demand/P4_full_fixed_TEAM_HIGH_DEMAND/results.xlsx
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1590,6 +1590,39 @@
       <c r="F21" t="inlineStr">
         <is>
           <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>undelivered_volume_paid</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>логическое</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>[true, false]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
         </is>
       </c>
     </row>
@@ -12101,18 +12134,18 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I29" t="b">
@@ -12125,7 +12158,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12150,18 +12183,18 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F30" t="n">
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I30" t="b">
@@ -12174,7 +12207,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12199,18 +12232,18 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F31" t="n">
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I31" t="b">
@@ -12223,7 +12256,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12248,18 +12281,18 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I32" t="b">
@@ -12272,7 +12305,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12297,18 +12330,18 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I33" t="b">
@@ -12321,7 +12354,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12346,18 +12379,18 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>emergency_share_of_demand</t>
+          <t>consecutive_years_with_emergency_as_base_channel</t>
         </is>
       </c>
       <c r="F34" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>&lt;= (иначе год считается базовым для Emergency)</t>
+          <t>&lt;=</t>
         </is>
       </c>
       <c r="I34" t="b">
@@ -12370,7 +12403,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>не более 2 базовых лет подряд</t>
+          <t>базовый канал = доля Emergency в спросе &gt; 20%; доля в этом году 0.000</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12428,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -12419,7 +12452,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2035-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12663,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -12654,7 +12687,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2036-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12865,7 +12898,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -12889,7 +12922,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2037-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13198,7 +13231,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -13222,7 +13255,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2038-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13531,7 +13564,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -13555,7 +13588,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2039-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13962,7 +13995,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>max_end_of_month_stock_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -13986,7 +14019,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>

--- a/results/demand/P4_full_fixed_TEAM_HIGH_DEMAND/results.xlsx
+++ b/results/demand/P4_full_fixed_TEAM_HIGH_DEMAND/results.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -917,7 +917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1622,6 +1622,105 @@
       <c r="F22" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exp10_demand_max</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>дополнительный относительный рост спроса</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exp10_isru_reduction_max</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>[0.0, 0.02]</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
+</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exp10_price_half_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>относительное отклонение переменной цены от обязательного стресса</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TEAM_ASSUMPTION</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>[-0.1, 0.1]</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
         </is>
       </c>

--- a/results/demand/P4_full_fixed_TEAM_HIGH_DEMAND/results.xlsx
+++ b/results/demand/P4_full_fixed_TEAM_HIGH_DEMAND/results.xlsx
@@ -7585,7 +7585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7694,6 +7694,11 @@
           <t>reservation_payment_mln</t>
         </is>
       </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -7769,6 +7774,9 @@
       <c r="U2" t="n">
         <v>1.93647</v>
       </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -7844,6 +7852,9 @@
       <c r="U3" t="n">
         <v>49.4442</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7919,6 +7930,9 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -7994,6 +8008,9 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -8069,6 +8086,9 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -8144,6 +8164,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -8219,6 +8242,9 @@
       <c r="U8" t="n">
         <v>68.8734</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -8294,6 +8320,9 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -8369,6 +8398,9 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -8444,6 +8476,9 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -8519,6 +8554,9 @@
       <c r="U12" t="n">
         <v>0</v>
       </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -8594,6 +8632,9 @@
       <c r="U13" t="n">
         <v>85.5</v>
       </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -8669,6 +8710,9 @@
       <c r="U14" t="n">
         <v>0</v>
       </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -8744,6 +8788,9 @@
       <c r="U15" t="n">
         <v>3.9567</v>
       </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -8819,6 +8866,9 @@
       <c r="U16" t="n">
         <v>0</v>
       </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -8894,6 +8944,9 @@
       <c r="U17" t="n">
         <v>0</v>
       </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -8969,6 +9022,9 @@
       <c r="U18" t="n">
         <v>72.7974</v>
       </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -9044,6 +9100,9 @@
       <c r="U19" t="n">
         <v>0</v>
       </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -9119,6 +9178,9 @@
       <c r="U20" t="n">
         <v>0</v>
       </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -9194,6 +9256,9 @@
       <c r="U21" t="n">
         <v>0</v>
       </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -9269,6 +9334,9 @@
       <c r="U22" t="n">
         <v>0</v>
       </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9344,6 +9412,9 @@
       <c r="U23" t="n">
         <v>85.5</v>
       </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9419,6 +9490,9 @@
       <c r="U24" t="n">
         <v>0</v>
       </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9494,6 +9568,9 @@
       <c r="U25" t="n">
         <v>6.7866</v>
       </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -9569,6 +9646,9 @@
       <c r="U26" t="n">
         <v>0</v>
       </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9644,6 +9724,9 @@
       <c r="U27" t="n">
         <v>0</v>
       </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -9719,6 +9802,9 @@
       <c r="U28" t="n">
         <v>85.5</v>
       </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -9794,6 +9880,9 @@
       <c r="U29" t="n">
         <v>0</v>
       </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9869,6 +9958,9 @@
       <c r="U30" t="n">
         <v>25.4211</v>
       </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -9944,6 +10036,9 @@
       <c r="U31" t="n">
         <v>0</v>
       </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -10017,6 +10112,9 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10031,7 +10129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10095,6 +10193,11 @@
           <t>cumulative_capex_mln</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>take_or_pay_topup_mln</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -10137,6 +10240,9 @@
       <c r="L2" t="n">
         <v>360</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -10179,6 +10285,9 @@
       <c r="L3" t="n">
         <v>1610</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -10221,6 +10330,9 @@
       <c r="L4" t="n">
         <v>1790</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -10263,6 +10375,9 @@
       <c r="L5" t="n">
         <v>1790</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -10305,6 +10420,9 @@
       <c r="L6" t="n">
         <v>1790</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -10346,6 +10464,9 @@
       </c>
       <c r="L7" t="n">
         <v>1790</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -23121,7 +23242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23559,11 +23680,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>opening_inventory_t</t>
+          <t>take_or_pay_topup_mln</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.328859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -23579,11 +23700,11 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>closing_inventory_t</t>
+          <t>opening_inventory_t</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>12.328859</v>
       </c>
     </row>
     <row r="24">
@@ -23599,11 +23720,11 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>closing_inventory_t</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -23619,11 +23740,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26">
@@ -23639,11 +23760,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>guideline_violations</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -23659,10 +23780,10 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
+          <t>warnings</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -23679,11 +23800,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>checks_total</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>75</v>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -23699,10 +23820,30 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="D30" t="n">
         <v>64</v>
       </c>
     </row>

--- a/results/demand/P4_full_fixed_TEAM_HIGH_DEMAND/results.xlsx
+++ b/results/demand/P4_full_fixed_TEAM_HIGH_DEMAND/results.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="kpi" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="investments" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="yearly_balance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="inventory_trace" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="source_schedule" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="financial_breakdown" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="constraint_checks" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="constraint_matrix" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="delivery_schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="kpi" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="investments" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="assumptions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="preparatory_period" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="contract_reserve_proof" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -578,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions</t>
+          <t>yearly_balance, inventory_trace, source_schedule, financial_breakdown, constraint_checks, constraint_matrix, delivery_schedule, kpi, investments, assumptions, preparatory_period, contract_reserve_proof</t>
         </is>
       </c>
     </row>
@@ -917,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1441,7 +1443,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>"end_of_month_hard_peak_warning"</t>
+          <t>"end_of_month_and_intra_month_peak_hard"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1461,24 +1463,24 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Жёсткое нарушение, если запас на конец месяца &gt; ёмкости; предупреждение, если запас после поступления (до выдачи) &gt; ёмкости.</t>
+          <t>Оба превышения ёмкости — жёсткие нарушения. Проверяется запас на конец месяца и расчётный пик внутри месяца при заявленном дроблении поставок (intra_month_delivery_batches): физическая исполнимость плана доказывается графиком поступлений, а не пометкой допущения.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>emergency_reserve_equivalence</t>
+          <t>intra_month_delivery_batches</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>"stock_covers_lead_time_and_reserved_capacity_covers_45d"</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>правило</t>
+          <t>партий в месяц</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1488,29 +1490,29 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>null</t>
+          <t>[1, 4]</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Контрактный резерв Emergency засчитывается, только если физический запас покрывает спрос за 6 недель срока поставки И зарезервированная мощность Emergency &gt;= R_y.</t>
+          <t>Месячный объём канала приходит N равными партиями, равномерно распределёнными по месяцу, при равномерной выдаче потребителям (конвенция организатора). Пик запаса после партии j равен I_нач + (j·нетто − (j−1)·выдача)/N, максимум берётся по j = 1..N. При N = 1 это запас сразу после единственного поступления, до выдачи, — консервативный край без допущения о внутримесячной синхронизации поставок и выдачи. При N → ∞ пик стремится к max(запас на начало, запас на конец). Выбрано N = 1: организатор не задаёт размер отдельной партии, и ни один принятый план команды не нуждается в дроблении. Чувствительность к N = 2 и N = 4 показана в results/intra_month/intra_month_capacity.md.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>opening_stock_reservation_years</t>
+          <t>emergency_reserve_equivalence</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>"contracted_batch_schedule_and_waiting_cover"</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>лет</t>
+          <t>правило</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1520,29 +1522,29 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>[0.0, 1.0]</t>
+          <t>null</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
+          <t>Договорный аварийный резерв засчитывается только при одновременном выполнении пяти условий, каждое из которых печатается отдельной строкой в contract_reserve_proof: (1) канал доступен в этом году; (2) договорный срок исполнения партии не быстрее срока поставки канала по данным организатора; (3) нетто-объём гарантированной партии после потерь хранилища &gt;= R_y; (4) зарезервированная мощность канала за вычетом обычных заказов года &gt;= партия × число активаций; (5) физический запас на начало года покрывает спрос за время активации плюс срок исполнения. Сам по себе лимит мощности канала (80 т/год) эквивалентности не доказывает. Если блок inventory_policy.emergency_contract не задан, эквивалентность не доказана и действует физический резерв. Правило следует кейсу, §«Начальный запас и резерв».</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>prep_period_holding_charged</t>
+          <t>opening_stock_reservation_years</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>логическое</t>
+          <t>лет</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1552,176 +1554,319 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>[true, false]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Стоимость хранения начисляется с 2035-01; время хранения в подготовительном периоде (&lt; 1 месяца) не оплачивается.</t>
+          <t>Закупка подготовительного периода оплачивает ставку резервирования источника на купленный тоннаж за один год; учитывается в 2035 году.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>intra_year_demand_profile</t>
+          <t>prep_period_holding_charged</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>"uniform"</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>перечисление</t>
+          <t>логическое</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CASE_INPUT</t>
+          <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>["uniform"]</t>
+          <t>[true, false]</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+          <t>Хранение начального запаса начисляется с фактического месяца поставки, а не с 2035-01: ранняя поставка начального запаса не хранится бесплатно. Правило то же, что и в основном периоде (трапеция): в месяц поставки средний запас равен половине поступления, в каждый последующий месяц подготовительного периода — полному нетто-запасу. Расход относится на первый финансовый год (2035), как закупка и плата за резерв подготовительного периода. Значение false выключает начисление и оставлено только для сопоставления с прежней версией расчёта.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>intra_year_demand_profile</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>"uniform"</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>перечисление</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CASE_INPUT</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>["uniform"]</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Конвенция организатора — равномерный спрос внутри года, 365 дней.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>undelivered_volume_paid</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>логическое</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>CASE_INPUT</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>[true, false]</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t xml:space="preserve">Контрольное правило организатора: оплачивается заказанный объём (Q_pay = max(заказ, TOP × резерв)), недопоставка в обязательном стрессе платёж не возвращает. Значение false (оплата по фактически поставленному объёму) допустимо только в отдельном исследовательском контрактном сценарии и не является условием организатора.
 </t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+    <row r="24">
+      <c r="A24" t="inlineStr">
         <is>
           <t>exp10_demand_max</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>дополнительный относительный рост спроса</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель общего и критического спроса обязательного стресса в 2038–2040. Одна постоянная реализация на прогон; в основной модели независима от ISRU и цены. Диагностика использует общую равномерную величину с ISRU. Диапазон охватывает цель 1 % из EXP-08; иллюстративная условная неопределённость, а не откалиброванные вероятности организатора. Ядро этот ключ не использует.
 </t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>exp10_isru_reduction_max</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>дополнительное относительное снижение фактической доли поставки ISRU</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>[0.0, 0.02]</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(0, value), множитель (1 − s) к долям ISRU обязательного стресса в 2038–2040. Одна постоянная реализация; надёжность повторно не умножается. Основная модель — независимая, диагностика — комонотонная связь спроса и ISRU; цена независима в обеих. Случайные отключения мощности Core не включены.
 </t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>exp10_price_half_range</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>относительное отклонение переменной цены от обязательного стресса</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>TEAM_ASSUMPTION</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>[-0.1, 0.1]</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t xml:space="preserve">Только EXP-10: равномерное U(−value, value), одна общая постоянная ценовая реализация для Core и Flex в 2038–2039, независимая от физических факторов. Умножает существующий стрессовый множитель 1,25. Иллюстративный экономический диапазон без эмпирической калибровки; не шок мощности или поставки.
 </t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>scenario_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>plan_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_mode</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>opening_t</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>arrived_t</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>closing_t</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>holding_cost_mln</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2034-12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>BASE</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="G2" t="n">
+        <v>12.328859</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.36986577</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>(empty)</t>
         </is>
       </c>
     </row>
@@ -2352,7 +2497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2458,6 +2603,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>peak_stock_t</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>delivery_batches</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>inflow_A_t</t>
         </is>
       </c>
@@ -2530,6 +2685,12 @@
         <v>0.7270604900000001</v>
       </c>
       <c r="U2" t="n">
+        <v>21.07315733333333</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2601,6 +2762,12 @@
         <v>0.7017183900000004</v>
       </c>
       <c r="U3" t="n">
+        <v>20.65078900000001</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2672,6 +2839,12 @@
         <v>0.6763762900000004</v>
       </c>
       <c r="U4" t="n">
+        <v>20.22842066666668</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2743,6 +2916,12 @@
         <v>0.6510341900000006</v>
       </c>
       <c r="U5" t="n">
+        <v>19.80605233333334</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2814,6 +2993,12 @@
         <v>0.6256920900000007</v>
       </c>
       <c r="U6" t="n">
+        <v>19.38368400000001</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2885,6 +3070,12 @@
         <v>0.6003499900000009</v>
       </c>
       <c r="U7" t="n">
+        <v>18.96131566666668</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -2956,6 +3147,12 @@
         <v>0.575007890000001</v>
       </c>
       <c r="U8" t="n">
+        <v>18.53894733333335</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3027,6 +3224,12 @@
         <v>0.5496657900000012</v>
       </c>
       <c r="U9" t="n">
+        <v>18.11657900000002</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3098,6 +3301,12 @@
         <v>0.5243236900000012</v>
       </c>
       <c r="U10" t="n">
+        <v>17.69421066666669</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3169,6 +3378,12 @@
         <v>0.4989815900000014</v>
       </c>
       <c r="U11" t="n">
+        <v>17.27184233333336</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3240,6 +3455,12 @@
         <v>0.4736394900000014</v>
       </c>
       <c r="U12" t="n">
+        <v>16.84947400000003</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3311,6 +3532,12 @@
         <v>0.4482973900000016</v>
       </c>
       <c r="U13" t="n">
+        <v>16.42710566666669</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
         <v>9.156333333333334</v>
       </c>
     </row>
@@ -3382,6 +3609,12 @@
         <v>0.4160375125000016</v>
       </c>
       <c r="U14" t="n">
+        <v>19.44081141666669</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3453,6 +3686,12 @@
         <v>0.3768598575000016</v>
       </c>
       <c r="U15" t="n">
+        <v>18.78785050000003</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3524,6 +3763,12 @@
         <v>0.3376822025000015</v>
       </c>
       <c r="U16" t="n">
+        <v>18.13488958333336</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3595,6 +3840,12 @@
         <v>0.2985045475000014</v>
       </c>
       <c r="U17" t="n">
+        <v>17.48192866666669</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3666,6 +3917,12 @@
         <v>0.2593268925000013</v>
       </c>
       <c r="U18" t="n">
+        <v>16.82896775000002</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3737,6 +3994,12 @@
         <v>0.2201492375000012</v>
       </c>
       <c r="U19" t="n">
+        <v>16.17600683333335</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3808,6 +4071,12 @@
         <v>0.1809715825000011</v>
       </c>
       <c r="U20" t="n">
+        <v>15.52304591666669</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3879,6 +4148,12 @@
         <v>0.1417939275000011</v>
       </c>
       <c r="U21" t="n">
+        <v>14.87008500000002</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -3950,6 +4225,12 @@
         <v>0.102616272500001</v>
       </c>
       <c r="U22" t="n">
+        <v>14.21712408333335</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4021,6 +4302,12 @@
         <v>0.06343861750000086</v>
       </c>
       <c r="U23" t="n">
+        <v>13.56416316666668</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4092,6 +4379,12 @@
         <v>0.02426096250000079</v>
       </c>
       <c r="U24" t="n">
+        <v>12.91120225000001</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4163,6 +4456,12 @@
         <v>0.002336067500000372</v>
       </c>
       <c r="U25" t="n">
+        <v>12.25824133333334</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
         <v>12.75431666666667</v>
       </c>
     </row>
@@ -4234,6 +4533,12 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
+        <v>16.17039425</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4305,6 +4610,12 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
+        <v>16.17039425</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4376,6 +4687,12 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
+        <v>16.17039425</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4447,6 +4764,12 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
+        <v>16.17039425</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4518,6 +4841,12 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
+        <v>16.17039425</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4589,6 +4918,12 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
+        <v>16.17039425</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4660,6 +4995,12 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
+        <v>16.7291618</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4731,6 +5072,12 @@
         <v>0</v>
       </c>
       <c r="U33" t="n">
+        <v>16.7291618</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4802,6 +5149,12 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
+        <v>16.7291618</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4873,6 +5226,12 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
+        <v>16.7291618</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -4944,6 +5303,12 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
+        <v>16.7291618</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5015,6 +5380,12 @@
         <v>0</v>
       </c>
       <c r="U37" t="n">
+        <v>16.7291618</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -5086,6 +5457,12 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
+        <v>13.3191786</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5157,6 +5534,12 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
+        <v>13.3191786</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5228,6 +5611,12 @@
         <v>0</v>
       </c>
       <c r="U40" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5299,6 +5688,12 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5370,6 +5765,12 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1</v>
+      </c>
+      <c r="W42" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5441,6 +5842,12 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1</v>
+      </c>
+      <c r="W43" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5512,6 +5919,12 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1</v>
+      </c>
+      <c r="W44" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5583,6 +5996,12 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1</v>
+      </c>
+      <c r="W45" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5654,6 +6073,12 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1</v>
+      </c>
+      <c r="W46" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5725,6 +6150,12 @@
         <v>0</v>
       </c>
       <c r="U47" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1</v>
+      </c>
+      <c r="W47" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5796,6 +6227,12 @@
         <v>0</v>
       </c>
       <c r="U48" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5867,6 +6304,12 @@
         <v>0</v>
       </c>
       <c r="U49" t="n">
+        <v>23.1991786</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1</v>
+      </c>
+      <c r="W49" t="n">
         <v>13.48095</v>
       </c>
     </row>
@@ -5938,6 +6381,12 @@
         <v>0</v>
       </c>
       <c r="U50" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V50" t="n">
+        <v>1</v>
+      </c>
+      <c r="W50" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6009,6 +6458,12 @@
         <v>0</v>
       </c>
       <c r="U51" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1</v>
+      </c>
+      <c r="W51" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6080,6 +6535,12 @@
         <v>0</v>
       </c>
       <c r="U52" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V52" t="n">
+        <v>1</v>
+      </c>
+      <c r="W52" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6151,6 +6612,12 @@
         <v>0</v>
       </c>
       <c r="U53" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1</v>
+      </c>
+      <c r="W53" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6222,6 +6689,12 @@
         <v>0</v>
       </c>
       <c r="U54" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1</v>
+      </c>
+      <c r="W54" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6293,6 +6766,12 @@
         <v>0</v>
       </c>
       <c r="U55" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6364,6 +6843,12 @@
         <v>0</v>
       </c>
       <c r="U56" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V56" t="n">
+        <v>1</v>
+      </c>
+      <c r="W56" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6435,6 +6920,12 @@
         <v>0</v>
       </c>
       <c r="U57" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V57" t="n">
+        <v>1</v>
+      </c>
+      <c r="W57" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6506,6 +6997,12 @@
         <v>0</v>
       </c>
       <c r="U58" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V58" t="n">
+        <v>1</v>
+      </c>
+      <c r="W58" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6577,6 +7074,12 @@
         <v>0</v>
       </c>
       <c r="U59" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V59" t="n">
+        <v>1</v>
+      </c>
+      <c r="W59" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6648,6 +7151,12 @@
         <v>0</v>
       </c>
       <c r="U60" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1</v>
+      </c>
+      <c r="W60" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6719,6 +7228,12 @@
         <v>0</v>
       </c>
       <c r="U61" t="n">
+        <v>27.38584506666667</v>
+      </c>
+      <c r="V61" t="n">
+        <v>1</v>
+      </c>
+      <c r="W61" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6790,6 +7305,12 @@
         <v>0</v>
       </c>
       <c r="U62" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V62" t="n">
+        <v>1</v>
+      </c>
+      <c r="W62" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6861,6 +7382,12 @@
         <v>0</v>
       </c>
       <c r="U63" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1</v>
+      </c>
+      <c r="W63" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -6932,6 +7459,12 @@
         <v>0</v>
       </c>
       <c r="U64" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V64" t="n">
+        <v>1</v>
+      </c>
+      <c r="W64" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7003,6 +7536,12 @@
         <v>0</v>
       </c>
       <c r="U65" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V65" t="n">
+        <v>1</v>
+      </c>
+      <c r="W65" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7074,6 +7613,12 @@
         <v>0</v>
       </c>
       <c r="U66" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1</v>
+      </c>
+      <c r="W66" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7145,6 +7690,12 @@
         <v>0</v>
       </c>
       <c r="U67" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V67" t="n">
+        <v>1</v>
+      </c>
+      <c r="W67" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7216,6 +7767,12 @@
         <v>0</v>
       </c>
       <c r="U68" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1</v>
+      </c>
+      <c r="W68" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7287,6 +7844,12 @@
         <v>0</v>
       </c>
       <c r="U69" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V69" t="n">
+        <v>1</v>
+      </c>
+      <c r="W69" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7358,6 +7921,12 @@
         <v>0</v>
       </c>
       <c r="U70" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V70" t="n">
+        <v>1</v>
+      </c>
+      <c r="W70" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7429,6 +7998,12 @@
         <v>0</v>
       </c>
       <c r="U71" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V71" t="n">
+        <v>1</v>
+      </c>
+      <c r="W71" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7500,6 +8075,12 @@
         <v>0</v>
       </c>
       <c r="U72" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V72" t="n">
+        <v>1</v>
+      </c>
+      <c r="W72" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -7571,6 +8152,12 @@
         <v>0</v>
       </c>
       <c r="U73" t="n">
+        <v>32.50000476666667</v>
+      </c>
+      <c r="V73" t="n">
+        <v>1</v>
+      </c>
+      <c r="W73" t="n">
         <v>15.83333333333333</v>
       </c>
     </row>
@@ -10220,7 +10807,7 @@
         <v>51.38067</v>
       </c>
       <c r="F2" t="n">
-        <v>7.05214728000001</v>
+        <v>7.42201305000001</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -10229,13 +10816,13 @@
         <v>360</v>
       </c>
       <c r="I2" t="n">
-        <v>1214.56123728</v>
+        <v>1214.93110305</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>1214.56123728</v>
+        <v>1214.93110305</v>
       </c>
       <c r="L2" t="n">
         <v>360</v>
@@ -10998,7 +11585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12689,7 +13276,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -12697,14 +13284,14 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>109.876</v>
+        <v>21.07315733333333</v>
       </c>
       <c r="G36" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -12721,7 +13308,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2035-01, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -12738,7 +13325,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -12746,14 +13333,14 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>109.876</v>
       </c>
       <c r="G37" t="n">
-        <v>109.876</v>
+        <v>190</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -12787,7 +13374,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -12795,18 +13382,19 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>all_deliveries_ordered_within_lead_time</t>
+          <t>ordered_A_t</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>109.876</v>
       </c>
       <c r="G38" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38">
-        <f>=</f>
-        <v/>
+        <v>109.876</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -12816,7 +13404,11 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -12831,7 +13423,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SOURCE_NOT_AVAILABLE</t>
+          <t>LEAD_TIME_VIOLATED</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12839,7 +13431,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>all_orders_from_available_sources</t>
+          <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -12875,27 +13467,26 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>STORAGE_OVERFLOW</t>
+          <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
+          <t>all_orders_from_available_sources</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6.60747808333336</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>70</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="H40">
+        <f>=</f>
+        <v/>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -12905,11 +13496,7 @@
           <t>hard</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>2036-01, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -12924,7 +13511,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12932,14 +13519,14 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>reserved_A_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>153.052</v>
+        <v>6.60747808333336</v>
       </c>
       <c r="G41" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -12956,7 +13543,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -12973,7 +13560,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12981,14 +13568,14 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>153.0518</v>
+        <v>19.44081141666669</v>
       </c>
       <c r="G42" t="n">
-        <v>153.052</v>
+        <v>70</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -13005,7 +13592,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2036-01, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13022,7 +13609,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -13030,170 +13617,170 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="G43" t="n">
+        <v>190</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>153.0518</v>
+      </c>
+      <c r="G44" t="n">
+        <v>153.052</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2036</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43">
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45">
         <f>=</f>
         <v/>
       </c>
-      <c r="I43" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" t="inlineStr">
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D44" t="n">
+      <c r="D46" t="n">
         <v>2036</v>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1</v>
-      </c>
-      <c r="G44" t="n">
-        <v>1</v>
-      </c>
-      <c r="H44">
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46">
         <f>=</f>
         <v/>
       </c>
-      <c r="I44" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" t="inlineStr">
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" t="n">
-        <v>70</v>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>1</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>2037-01, хранилище BASE; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>2037</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>190</v>
-      </c>
-      <c r="G46" t="n">
-        <v>190</v>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I46" t="b">
-        <v>1</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -13208,7 +13795,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -13216,14 +13803,14 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ordered_A_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>190</v>
+        <v>70</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -13240,7 +13827,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Earth-Core</t>
+          <t>2037-01, хранилище BASE; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13257,7 +13844,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -13265,14 +13852,14 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>reserved_C_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>13.189</v>
+        <v>16.17039425</v>
       </c>
       <c r="G48" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -13289,7 +13876,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2037-01, хранилище BASE; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13306,7 +13893,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -13314,14 +13901,14 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>13.1882</v>
+        <v>190</v>
       </c>
       <c r="G49" t="n">
-        <v>13.189</v>
+        <v>190</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -13338,7 +13925,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -13355,7 +13942,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -13363,219 +13950,219 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>190</v>
+      </c>
+      <c r="G50" t="n">
+        <v>190</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="G51" t="n">
+        <v>130</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>13.1882</v>
+      </c>
+      <c r="G52" t="n">
+        <v>13.189</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2037</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1</v>
-      </c>
-      <c r="H50">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53">
         <f>=</f>
         <v/>
       </c>
-      <c r="I50" t="b">
-        <v>1</v>
-      </c>
-      <c r="J50" t="inlineStr">
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
+      <c r="D54" t="n">
         <v>2037</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="n">
-        <v>1</v>
-      </c>
-      <c r="H51">
+      <c r="F54" t="n">
+        <v>1</v>
+      </c>
+      <c r="G54" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54">
         <f>=</f>
         <v/>
       </c>
-      <c r="I51" t="b">
-        <v>1</v>
-      </c>
-      <c r="J51" t="inlineStr">
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>120</v>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I52" t="b">
-        <v>1</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>2038-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="G53" t="n">
-        <v>190</v>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I53" t="b">
-        <v>1</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>2038</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>161.7714</v>
-      </c>
-      <c r="G54" t="n">
-        <v>161.772</v>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I54" t="b">
-        <v>1</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
+      <c r="K54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -13590,7 +14177,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -13598,11 +14185,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>120</v>
@@ -13622,7 +14209,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -13639,7 +14226,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -13647,14 +14234,14 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>100</v>
+        <v>23.1991786</v>
       </c>
       <c r="G56" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -13671,7 +14258,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2038-03, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -13688,7 +14275,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -13696,268 +14283,268 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="G57" t="n">
+        <v>190</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>161.7714</v>
+      </c>
+      <c r="G58" t="n">
+        <v>161.772</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>120</v>
+      </c>
+      <c r="G59" t="n">
+        <v>120</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" t="n">
+        <v>100</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2038</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" t="n">
-        <v>1</v>
-      </c>
-      <c r="H57">
+      <c r="F61" t="n">
+        <v>1</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1</v>
+      </c>
+      <c r="H61">
         <f>=</f>
         <v/>
       </c>
-      <c r="I57" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" t="inlineStr">
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
+      <c r="K61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D58" t="n">
+      <c r="D62" t="n">
         <v>2038</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>1</v>
-      </c>
-      <c r="G58" t="n">
-        <v>1</v>
-      </c>
-      <c r="H58">
+      <c r="F62" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" t="n">
+        <v>1</v>
+      </c>
+      <c r="H62">
         <f>=</f>
         <v/>
       </c>
-      <c r="I58" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" t="inlineStr">
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" t="n">
-        <v>120</v>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I59" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>2039-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>190</v>
-      </c>
-      <c r="G60" t="n">
-        <v>190</v>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I60" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>190</v>
-      </c>
-      <c r="G61" t="n">
-        <v>190</v>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I61" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>2039</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>reserved_C_t_per_year</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>22.622</v>
-      </c>
-      <c r="G62" t="n">
-        <v>130</v>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I62" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Earth-New</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -13972,7 +14559,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -13980,14 +14567,14 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ordered_C_t</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>22.6216</v>
+        <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>22.622</v>
+        <v>120</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -14004,7 +14591,7 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Earth-New</t>
+          <t>2039-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14021,7 +14608,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -14029,11 +14616,11 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>120</v>
+        <v>27.38584506666667</v>
       </c>
       <c r="G64" t="n">
         <v>120</v>
@@ -14053,7 +14640,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2039-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14657,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -14078,14 +14665,14 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>reserved_A_t_per_year</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="G65" t="n">
-        <v>120</v>
+        <v>190</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -14102,7 +14689,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>Earth-Core</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14706,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -14127,317 +14714,317 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>190</v>
+      </c>
+      <c r="G66" t="n">
+        <v>190</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="G67" t="n">
+        <v>130</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>22.6216</v>
+      </c>
+      <c r="G68" t="n">
+        <v>22.622</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>120</v>
+      </c>
+      <c r="G69" t="n">
+        <v>120</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>120</v>
+      </c>
+      <c r="G70" t="n">
+        <v>120</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2039</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="n">
-        <v>1</v>
-      </c>
-      <c r="H66">
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71">
         <f>=</f>
         <v/>
       </c>
-      <c r="I66" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" t="inlineStr">
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
+      <c r="K71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D67" t="n">
+      <c r="D72" t="n">
         <v>2039</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E72" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>1</v>
-      </c>
-      <c r="G67" t="n">
-        <v>1</v>
-      </c>
-      <c r="H67">
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72">
         <f>=</f>
         <v/>
       </c>
-      <c r="I67" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" t="inlineStr">
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>STORAGE_OVERFLOW</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>end_of_month_stock_t_in_worst_month</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" t="n">
-        <v>120</v>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I68" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>2040-01, хранилище ZBO; проверка помесячная</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>reserved_A_t_per_year</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>190</v>
-      </c>
-      <c r="G69" t="n">
-        <v>190</v>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I69" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>ordered_A_t</t>
-        </is>
-      </c>
-      <c r="F70" t="n">
-        <v>190</v>
-      </c>
-      <c r="G70" t="n">
-        <v>190</v>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I70" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Earth-Core</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>CAPACITY_EXCEEDED</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>reserved_C_t_per_year</t>
-        </is>
-      </c>
-      <c r="F71" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="G71" t="n">
-        <v>130</v>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I71" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Earth-New</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>2040</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>ordered_C_t</t>
-        </is>
-      </c>
-      <c r="F72" t="n">
-        <v>84.73690000000001</v>
-      </c>
-      <c r="G72" t="n">
-        <v>84.73699999999999</v>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>&lt;=</t>
-        </is>
-      </c>
-      <c r="I72" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>hard</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Earth-New</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -14452,7 +15039,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CAPACITY_EXCEEDED</t>
+          <t>STORAGE_OVERFLOW</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -14460,11 +15047,11 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>reserved_D_t_per_year</t>
+          <t>end_of_month_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
         <v>120</v>
@@ -14484,7 +15071,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; проверка помесячная</t>
         </is>
       </c>
     </row>
@@ -14501,7 +15088,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ORDER_EXCEEDS_RESERVATION</t>
+          <t>INTRA_MONTH_PEAK</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -14509,11 +15096,11 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ordered_D_t</t>
+          <t>intra_month_peak_stock_t_in_worst_month</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>120</v>
+        <v>32.50000476666667</v>
       </c>
       <c r="G74" t="n">
         <v>120</v>
@@ -14533,7 +15120,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Lunar-ISRU</t>
+          <t>2040-01, хранилище ZBO; поставка одной партией в начале месяца</t>
         </is>
       </c>
     </row>
@@ -14550,7 +15137,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>LEAD_TIME_VIOLATED</t>
+          <t>CAPACITY_EXCEEDED</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -14558,72 +15145,366 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
+          <t>reserved_A_t_per_year</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>190</v>
+      </c>
+      <c r="G75" t="n">
+        <v>190</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>ordered_A_t</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>190</v>
+      </c>
+      <c r="G76" t="n">
+        <v>190</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Earth-Core</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>reserved_C_t_per_year</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="G77" t="n">
+        <v>130</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>ordered_C_t</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>84.73690000000001</v>
+      </c>
+      <c r="G78" t="n">
+        <v>84.73699999999999</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Earth-New</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CAPACITY_EXCEEDED</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>reserved_D_t_per_year</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>120</v>
+      </c>
+      <c r="G79" t="n">
+        <v>120</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ORDER_EXCEEDS_RESERVATION</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>ordered_D_t</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>120</v>
+      </c>
+      <c r="G80" t="n">
+        <v>120</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>hard</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Lunar-ISRU</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LEAD_TIME_VIOLATED</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2040</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>all_deliveries_ordered_within_lead_time</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="n">
-        <v>1</v>
-      </c>
-      <c r="H75">
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81">
         <f>=</f>
         <v/>
       </c>
-      <c r="I75" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" t="inlineStr">
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>TEAM_HIGH_DEMAND</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>P4_full</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
+      <c r="K81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>SOURCE_NOT_AVAILABLE</t>
         </is>
       </c>
-      <c r="D76" t="n">
+      <c r="D82" t="n">
         <v>2040</v>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>all_orders_from_available_sources</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>1</v>
-      </c>
-      <c r="G76" t="n">
-        <v>1</v>
-      </c>
-      <c r="H76">
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82">
         <f>=</f>
         <v/>
       </c>
-      <c r="I76" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" t="inlineStr">
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" t="inlineStr">
         <is>
           <t>hard</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23242,7 +24123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23284,7 +24165,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10695.10582496</v>
+        <v>10695.47569073</v>
       </c>
     </row>
     <row r="3">
@@ -23304,7 +24185,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8764.364906731</v>
+        <v>8764.734772501</v>
       </c>
     </row>
     <row r="4">
@@ -23444,7 +24325,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>7.437059549150628</v>
+        <v>7.43731674284293</v>
       </c>
     </row>
     <row r="11">
@@ -23464,7 +24345,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.094479548741465</v>
+        <v>6.094736742433768</v>
       </c>
     </row>
     <row r="12">
@@ -23624,7 +24505,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9.476124960000025</v>
+        <v>9.845990730000024</v>
       </c>
     </row>
     <row r="20">
@@ -23740,11 +24621,11 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hard_violations</t>
+          <t>prep_holding_mln</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6</v>
+        <v>0.36986577</v>
       </c>
     </row>
     <row r="26">
@@ -23760,11 +24641,11 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>guideline_violations</t>
+          <t>prep_holding_months</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -23780,11 +24661,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>warnings</t>
+          <t>hard_violations</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -23800,11 +24681,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>feasible</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
+          <t>guideline_violations</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -23820,11 +24701,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>checks_total</t>
+          <t>warnings</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -23840,11 +24721,51 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>feasible</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>checks_total</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TEAM_HIGH_DEMAND</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>P4_full</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
           <t>checks_passed</t>
         </is>
       </c>
-      <c r="D30" t="n">
-        <v>64</v>
+      <c r="D32" t="n">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
